--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-quantite-subordonnee.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -788,6 +788,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -6780,7 +6784,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -6788,10 +6792,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6817,10 +6821,10 @@
         <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6851,7 +6855,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6869,7 +6873,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6889,10 +6893,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6915,13 +6919,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6972,7 +6976,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6992,10 +6996,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7018,7 +7022,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7051,7 +7055,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7069,7 +7073,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7093,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7115,7 +7119,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7168,7 +7172,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7188,10 +7192,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7247,25 +7251,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7285,10 +7289,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7311,7 +7315,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7364,7 +7368,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7384,10 +7388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7410,13 +7414,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7447,7 +7451,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7465,7 +7469,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7485,10 +7489,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7511,13 +7515,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7548,7 +7552,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7566,7 +7570,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7586,10 +7590,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7615,10 +7619,10 @@
         <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7669,7 +7673,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7689,10 +7693,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7790,10 +7794,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7893,10 +7897,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7996,10 +8000,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8099,10 +8103,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8202,10 +8206,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8305,10 +8309,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8406,10 +8410,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8507,10 +8511,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8610,10 +8614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8641,10 +8645,10 @@
         <v>198</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8715,10 +8719,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8816,17 +8820,17 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
@@ -8844,11 +8848,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8899,7 +8903,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8919,10 +8923,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8947,11 +8951,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9002,7 +9006,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9022,10 +9026,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9123,10 +9127,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9167,7 +9171,7 @@
         <v>74</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>74</v>
@@ -9226,10 +9230,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9270,7 +9274,7 @@
         <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>74</v>
@@ -9329,10 +9333,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9373,7 +9377,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -9432,10 +9436,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9535,10 +9539,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9579,7 +9583,7 @@
         <v>74</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>74</v>
@@ -9638,10 +9642,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9739,10 +9743,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9840,10 +9844,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9943,10 +9947,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10046,10 +10050,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10149,10 +10153,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10180,10 +10184,10 @@
         <v>160</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10214,7 +10218,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10232,7 +10236,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10252,10 +10256,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10355,10 +10359,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10381,7 +10385,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10434,7 +10438,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10454,10 +10458,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10480,7 +10484,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10533,7 +10537,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10553,10 +10557,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10579,7 +10583,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10632,7 +10636,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10652,10 +10656,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10678,7 +10682,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10731,7 +10735,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10751,10 +10755,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10777,7 +10781,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10830,7 +10834,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10850,10 +10854,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10876,7 +10880,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10929,7 +10933,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10949,10 +10953,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10975,7 +10979,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11028,7 +11032,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11048,10 +11052,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11074,7 +11078,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11127,7 +11131,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11147,10 +11151,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11173,7 +11177,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11226,7 +11230,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11246,10 +11250,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11272,7 +11276,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11325,7 +11329,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11345,10 +11349,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11371,11 +11375,11 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11426,7 +11430,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11446,10 +11450,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11547,10 +11551,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11648,10 +11652,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11749,10 +11753,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11850,10 +11854,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11953,10 +11957,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12056,10 +12060,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12159,10 +12163,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12262,10 +12266,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12363,10 +12367,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12400,7 +12404,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>74</v>
@@ -12422,7 +12426,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12440,7 +12444,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12460,10 +12464,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12486,7 +12490,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12539,7 +12543,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -12559,10 +12563,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12585,7 +12589,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12638,7 +12642,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
